--- a/tests/realSuite/Piano-viaggi_Tennistavolo_IS_28-nov-25-CON-VETTORE/input.xlsx
+++ b/tests/realSuite/Piano-viaggi_Tennistavolo_IS_28-nov-25-CON-VETTORE/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,90 +466,150 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IS MEZZOLOMBARDO MARTINI</t>
+          <t>IS CLES RUSSELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Via Perlasca, 4, Mezzolombardo</t>
+          <t>Piazza Fiera, Cles</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IS PRIMIERO</t>
+          <t>IS MEZZOLOMBARDO MARTINI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Via delle Fonti, 10, Transacqua, Fiera di Primiero</t>
+          <t>Via Perlasca, 4, Mezzolombardo</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IS RIVA DEL GARDA MAFFEI</t>
+          <t>IS PRIMIERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fermata Autobus - Viale dei Martiri, Riva del Garda</t>
+          <t>Loc. Ponte Serra (fermata corriere), Lamon BL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IS ROVERETO DON MILANI</t>
+          <t>IS PRIMIERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Piazzale Orsi (fermata autobus I.P.I.A.), Rovereto</t>
+          <t>Via delle Fonti, 10, Transacqua, Fiera di Primiero</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IS ROVERETO MARCONI</t>
+          <t>IS RIVA DEL GARDA MAFFEI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viale Nazionale, fermata bus di fronte I.T.I., Rovereto</t>
+          <t>Fermata Autobus - Viale dei Martiri, Riva del Garda</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>IS ROVERETO DON MILANI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Piazzale Orsi (fermata autobus I.P.I.A.), Rovereto</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IS ROVERETO MARCONI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Viale Nazionale, fermata bus di fronte I.T.I., Rovereto</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IS ROVERETO ROSMINI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Piazzale Orsi (fermata autobus I.P.I.A.), Rovereto</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IS TIONE ENAIP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Via Durone, Tione</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>IS TIONE GUETTI</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Via Durone, Tione</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C13" t="n">
         <v>13</v>
       </c>
     </row>
